--- a/artfynd/A 32268-2022 artfynd.xlsx
+++ b/artfynd/A 32268-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32268-2022 artfynd.xlsx
+++ b/artfynd/A 32268-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>103262651</v>
       </c>
       <c r="B2" t="n">
-        <v>75910</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>77726</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>371765.6256274984</v>
+        <v>371765</v>
       </c>
       <c r="R2" t="n">
-        <v>6242454.767930272</v>
+        <v>6242455</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-08-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -796,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103262654</v>
+        <v>103262645</v>
       </c>
       <c r="B3" t="n">
-        <v>57577</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208249</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>371742.3570556467</v>
+        <v>371714</v>
       </c>
       <c r="R3" t="n">
-        <v>6242383.874722542</v>
+        <v>6242413</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,19 +849,9 @@
           <t>2022-08-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-08-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,15 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103262646</v>
+        <v>103262653</v>
       </c>
       <c r="B4" t="n">
-        <v>93054</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,21 +893,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2810</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -952,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>371714.3155361687</v>
+        <v>371733</v>
       </c>
       <c r="R4" t="n">
-        <v>6242413.024183003</v>
+        <v>6242353</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,19 +950,9 @@
           <t>2022-08-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-08-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,15 +983,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103262653</v>
+        <v>103262696</v>
       </c>
       <c r="B5" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1068,10 +1018,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>371732.5481164024</v>
+        <v>371645</v>
       </c>
       <c r="R5" t="n">
-        <v>6242353.645234338</v>
+        <v>6242538</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,19 +1051,9 @@
           <t>2022-08-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-08-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,15 +1084,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103262645</v>
+        <v>103277748</v>
       </c>
       <c r="B6" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,10 +1119,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>371714.3155361687</v>
+        <v>371674</v>
       </c>
       <c r="R6" t="n">
-        <v>6242413.024183003</v>
+        <v>6242471</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,22 +1149,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,48 +1185,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103262738</v>
+        <v>103316321</v>
       </c>
       <c r="B7" t="n">
-        <v>83939</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>258917</v>
+        <v>2180</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypoxylon petriniae</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>M.Stadler &amp; J.Fourn.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Söndrebalj, Sk</t>
+          <t>Lyckorna, Sk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>371606.5587356932</v>
+        <v>371776</v>
       </c>
       <c r="R7" t="n">
-        <v>6242399.067067017</v>
+        <v>6242258</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,22 +1250,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,7 +1264,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1375,15 +1286,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103262696</v>
+        <v>103316319</v>
       </c>
       <c r="B8" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96441</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1391,34 +1297,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>2668</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Söndrebalj, Sk</t>
+          <t>Lyckorna, Sk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>371644.6816647402</v>
+        <v>371801</v>
       </c>
       <c r="R8" t="n">
-        <v>6242538.329462248</v>
+        <v>6242261</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1445,22 +1351,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,15 +1387,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103277744</v>
+        <v>103277739</v>
       </c>
       <c r="B9" t="n">
-        <v>101323</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96222</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,21 +1398,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222395</v>
+        <v>2755</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Skuggsprötmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Eurhynchium striatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1531,10 +1422,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>371801.5057125512</v>
+        <v>371712</v>
       </c>
       <c r="R9" t="n">
-        <v>6242390.418521165</v>
+        <v>6242341</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,19 +1455,9 @@
           <t>2022-08-30</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-08-30</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1607,15 +1488,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103277748</v>
+        <v>103262646</v>
       </c>
       <c r="B10" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1623,21 +1499,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>2810</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1647,10 +1523,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>371673.2691501333</v>
+        <v>371714</v>
       </c>
       <c r="R10" t="n">
-        <v>6242471.979932165</v>
+        <v>6242413</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,22 +1553,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-08-30</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-08-30</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1723,15 +1589,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103277739</v>
+        <v>103277738</v>
       </c>
       <c r="B11" t="n">
-        <v>92931</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1739,21 +1600,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2755</v>
+        <v>2810</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skuggsprötmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Eurhynchium striatum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1763,10 +1624,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>371712.1605780206</v>
+        <v>371725</v>
       </c>
       <c r="R11" t="n">
-        <v>6242341.494351449</v>
+        <v>6242317</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1796,19 +1657,9 @@
           <t>2022-08-30</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-08-30</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1839,15 +1690,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103277738</v>
+        <v>103316314</v>
       </c>
       <c r="B12" t="n">
-        <v>93054</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,14 +1721,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Söndrebalj, Sk</t>
+          <t>Lyckorna, Sk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>371725.3168642162</v>
+        <v>371877</v>
       </c>
       <c r="R12" t="n">
-        <v>6242316.67783138</v>
+        <v>6242304</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1909,22 +1755,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-08-30</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-08-30</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1958,12 +1794,7 @@
         <v>103277741</v>
       </c>
       <c r="B13" t="n">
-        <v>57549</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58790</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1995,10 +1826,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>371774.4007311511</v>
+        <v>371775</v>
       </c>
       <c r="R13" t="n">
-        <v>6242376.80472094</v>
+        <v>6242377</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2028,19 +1859,9 @@
           <t>2022-08-30</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-08-30</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2071,15 +1892,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>103316314</v>
+        <v>103262654</v>
       </c>
       <c r="B14" t="n">
-        <v>93054</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2087,34 +1903,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2810</v>
+        <v>208249</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lyckorna, Sk</t>
+          <t>Söndrebalj, Sk</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>371877.332158612</v>
+        <v>371742</v>
       </c>
       <c r="R14" t="n">
-        <v>6242304.331276424</v>
+        <v>6242383</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2141,22 +1957,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2180,6 +1986,107 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr">
+        <is>
+          <t>Kartläggning av Ängelholms kommun 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>103277744</v>
+      </c>
+      <c r="B15" t="n">
+        <v>104253</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222395</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dvärghäxört</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Circaea alpina</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Söndrebalj, Sk</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>371802</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6242390</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hjärnarp</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-08-30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-08-30</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
         <is>
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>

--- a/artfynd/A 32268-2022 artfynd.xlsx
+++ b/artfynd/A 32268-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103262651</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103262645</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103262653</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103262696</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103277748</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1283,6 +1313,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103316321</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1384,6 +1419,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103316319</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1485,6 +1525,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103277739</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1586,6 +1631,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103262646</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1687,6 +1737,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103277738</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1788,6 +1843,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103316314</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1889,6 +1949,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103277741</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1990,6 +2055,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103262654</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2091,8 +2161,29 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103277744</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>